--- a/help.xlsx
+++ b/help.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/svinukonda/Documents/personal/cfc_songbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F445FC-5BE2-9248-807A-984284CAC649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94659B02-F075-894A-AD8E-C09B151ABA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{FAF232CC-24EA-EB42-A18E-7ABA36D52A3B}"/>
+    <workbookView xWindow="5180" yWindow="1960" windowWidth="28040" windowHeight="17180" xr2:uid="{FAF232CC-24EA-EB42-A18E-7ABA36D52A3B}"/>
   </bookViews>
   <sheets>
     <sheet name="git help" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>cannot pull with rebase: You have unstaged changes.</t>
   </si>
@@ -51,18 +51,37 @@
 git status
 git branch -a</t>
   </si>
+  <si>
+    <t>git pull
+python3 -m mkdocs gh-deploy</t>
+  </si>
+  <si>
+    <t>get the code from git main branch and push the code to mkdocs</t>
+  </si>
+  <si>
+    <t>python3 -m mkdocs serve</t>
+  </si>
+  <si>
+    <t>start mkdocs serve</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -85,13 +104,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,11 +449,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE245982-4F55-D244-BA4E-F793679D957C}">
-  <dimension ref="B2:C2"/>
+  <dimension ref="B2:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="2" max="2" width="50.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53" style="1" customWidth="1"/>
     <col min="3" max="3" width="65.83203125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="1"/>
   </cols>
@@ -442,6 +464,22 @@
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="34" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
